--- a/data/trans_camb/IP19C08-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-1.43446056022247</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.23050300716769</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.243605231045747</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.223585566761045</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-1.350394722221727</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-2.248822463300965</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-4.866552786694189</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.498485167177488</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.120044309233234</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-5.592200189638528</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-3.951347397052134</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-4.381929555603137</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>1.195607420243455</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.2193205852848757</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.148350426717493</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2.507282561394443</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.6939548143573369</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.3537234267382719</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.4968019266660484</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.7724981934835946</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.3474770381416895</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.6212943685859388</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.4171992432211775</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.6947650300975473</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -701,13 +706,16 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="n">
+        <v>-0.8432726081717652</v>
+      </c>
       <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n">
+        <v>-0.8055346640558445</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -718,13 +726,16 @@
       </c>
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="n">
+        <v>1.667981161466016</v>
+      </c>
       <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>0.4563339310577713</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.5155009536177176</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +748,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-0.7032399470978244</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.425954306523163</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.039663920693677</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.9251805950781185</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.2342611056433332</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.3206352659858788</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +774,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-5.023924275844753</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.272635029205286</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.739325351715675</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.2326741468496</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-2.922249543873567</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-2.927801916227388</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +800,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>3.46352066260538</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>12.91207251801589</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.774658124136307</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.617207587290663</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>3.395687320771801</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>6.06443856302097</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +826,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.1931639644107741</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.3916771054507726</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.2477727322230645</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.2204890631285135</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.05995044546217937</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.08205470973915746</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +852,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.8491896807988862</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.7912958946456528</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.6406591004899784</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.8444945784701563</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.560756753648249</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6367059384439427</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +878,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>2.677973875323323</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>9.085738568272463</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>3.000129227615799</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>2.126724661150081</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.555708327065153</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.517793751099241</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +908,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-1.465544575435435</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.300207190168627</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.312068888726105</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-3.487628368433187</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-1.378845665606744</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-2.305028343124245</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +934,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-6.42475461013921</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-5.844095370416015</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-6.882226762099592</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-8.741429302053485</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-5.147866963711576</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-5.792257826612001</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +960,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>2.809439845975664</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.95970512941348</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.613014582304931</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.2680686578036015</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.493132668660037</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.7446245208185828</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +986,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.35640564483205</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.3161972619561121</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.2531737612114958</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.6729646585869653</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.2977353944257509</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.4977268595181313</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1012,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.8567501977097727</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.8565086463918443</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.9532604826410447</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.7716793820471773</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.8112420155446737</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1038,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>2.689102761041739</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>3.172691701696151</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>2.025803789678795</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.6164346429110789</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1.103951855572432</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.4446077739002542</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1068,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.656112956520067</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-2.331445378780014</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.08690425206716382</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-3.09787899412299</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.3915115635959955</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-2.695378848050373</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1094,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-9.808711142725883</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-10.24959585330526</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-8.036235842280327</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-11.44678101833426</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-5.616795312872126</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-8.17928264024737</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1120,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>6.563374009173792</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.366112051459659</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>8.141027965591444</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.908210181400811</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>5.597471167521106</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>1.437285500606193</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1146,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.1063470580558103</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.3778958403231678</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.01605772970872589</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.5724104675513616</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.06729593802386952</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.4633018913750981</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1172,20 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.8781437981968007</v>
+      </c>
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
+        <v>-0.711060203863019</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.8243938895088209</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1194,20 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>3.43282944041794</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>1.993542790323347</v>
+      </c>
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>2.124039970918453</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.7286148040973726</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1220,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-1.17240116505535</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-0.4005919686090937</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.5148441950101514</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-2.098304835968264</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.8408335201090945</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-1.192718148866698</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1246,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-3.408513314804265</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-2.766802151361987</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-3.039911180453324</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-4.457414422672351</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-2.593001598210908</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-2.809603782886133</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1272,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>0.7724047252441801</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3.011122228956457</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>2.215789087655069</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.03278896194322913</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.7135164025566577</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0.8446074419397737</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1298,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.3049562144872219</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.1041989840527375</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.1178515331297687</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.4803170440478441</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.2050791345200676</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.2909037280818962</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1324,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.6774307651097631</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.6009815791551126</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.525268533869921</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.7612018310148639</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.5178864158953859</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.5834230283697144</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1350,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.2748150668873127</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>1.186281210899733</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.7693671508810012</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.06363727886207296</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.2205939652608607</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.2784644210488567</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1378,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
